--- a/artfynd/S 713-2026 artfynd.xlsx
+++ b/artfynd/S 713-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136439956</v>
       </c>
       <c r="B4" t="n">
-        <v>99377</v>
+        <v>99380</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136439960</v>
       </c>
       <c r="B5" t="n">
-        <v>110322</v>
+        <v>110325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 713-2026 artfynd.xlsx
+++ b/artfynd/S 713-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136439956</v>
       </c>
       <c r="B4" t="n">
-        <v>99380</v>
+        <v>99381</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136439960</v>
       </c>
       <c r="B5" t="n">
-        <v>110325</v>
+        <v>110326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 713-2026 artfynd.xlsx
+++ b/artfynd/S 713-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136439956</v>
       </c>
       <c r="B4" t="n">
-        <v>99381</v>
+        <v>99386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136439960</v>
       </c>
       <c r="B5" t="n">
-        <v>110326</v>
+        <v>110331</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 713-2026 artfynd.xlsx
+++ b/artfynd/S 713-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136439956</v>
       </c>
       <c r="B4" t="n">
-        <v>99386</v>
+        <v>99388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136439960</v>
       </c>
       <c r="B5" t="n">
-        <v>110331</v>
+        <v>110333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 713-2026 artfynd.xlsx
+++ b/artfynd/S 713-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136439956</v>
       </c>
       <c r="B4" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Maria Magnusson, Emilia Fagerberg</t>
+          <t>Emilia Fagerberg, Maria Magnusson, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1025,7 +1025,7 @@
         <v>136439960</v>
       </c>
       <c r="B5" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Emilia Fagerberg, Maria Magnusson</t>
+          <t>Maria Magnusson, Emilia Fagerberg, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/S 713-2026 artfynd.xlsx
+++ b/artfynd/S 713-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136439956</v>
       </c>
       <c r="B4" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emilia Fagerberg, Maria Magnusson, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Maria Magnusson, Emilia Fagerberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1025,7 +1025,7 @@
         <v>136439960</v>
       </c>
       <c r="B5" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maria Magnusson, Emilia Fagerberg, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Emilia Fagerberg, Maria Magnusson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/S 713-2026 artfynd.xlsx
+++ b/artfynd/S 713-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136439956</v>
       </c>
       <c r="B4" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136439960</v>
       </c>
       <c r="B5" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
